--- a/10_Paldea_Data.xlsx
+++ b/10_Paldea_Data.xlsx
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>Ok</v>
@@ -574,7 +574,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>Ok</v>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>Ok</v>
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>Ok</v>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>Ok</v>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>Ok</v>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>Ok</v>
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>Ok</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>Ok</v>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>Ok</v>
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>Ok</v>
@@ -954,7 +954,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>Ok</v>
@@ -992,7 +992,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>Ok</v>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>Ok</v>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>Ok</v>
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Ok</v>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>Ok</v>
@@ -1182,7 +1182,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>Ok</v>
@@ -1220,7 +1220,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>Ok</v>
@@ -1258,7 +1258,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>Ok</v>
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>Ok</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>Ok</v>
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>Ok</v>
@@ -1410,7 +1410,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>Ok</v>
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>Ok</v>
@@ -1486,7 +1486,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>Ok</v>
@@ -1524,7 +1524,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>Ok</v>
@@ -1562,7 +1562,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>Ok</v>
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v>Ok</v>
@@ -1638,7 +1638,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v>Ok</v>
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v>Ok</v>
@@ -1714,7 +1714,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v>Ok</v>
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H36" t="str">
         <v>Ok</v>
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H37" t="str">
         <v>Ok</v>
@@ -1828,7 +1828,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H38" t="str">
         <v>Ok</v>
@@ -1866,7 +1866,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v>Ok</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>Ok</v>
@@ -1942,7 +1942,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>Ok</v>
@@ -1980,7 +1980,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v>Ok</v>
@@ -2018,7 +2018,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>Ok</v>
@@ -2056,7 +2056,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H44" t="str">
         <v>Ok</v>
@@ -2094,7 +2094,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H45" t="str">
         <v>Ok</v>
@@ -2132,7 +2132,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H46" t="str">
         <v>Ok</v>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v>Ok</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H48" t="str">
         <v>Ok</v>
@@ -2246,7 +2246,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>Ok</v>
@@ -2284,7 +2284,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v>Ok</v>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>Ok</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v>Ok</v>
@@ -2398,7 +2398,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>Ok</v>
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>Ok</v>
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v>NONONO</v>
@@ -2512,7 +2512,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v>Ok</v>
@@ -2550,7 +2550,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v>Ok</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v>Ok</v>
@@ -2626,7 +2626,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>Ok</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v>Ok</v>
@@ -2702,7 +2702,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v>Ok</v>
@@ -2740,7 +2740,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H62" t="str">
         <v>Ok</v>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H63" t="str">
         <v>Ok</v>
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H64" t="str">
         <v>Ok</v>
@@ -2854,7 +2854,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H65" t="str">
         <v>Ok</v>
@@ -2892,7 +2892,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v>Ok</v>
@@ -2930,7 +2930,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H67" t="str">
         <v>Ok</v>
@@ -2968,7 +2968,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H68" t="str">
         <v>Ok</v>
@@ -3006,7 +3006,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v>Ok</v>
@@ -3044,7 +3044,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H70" t="str">
         <v>Ok</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H71" t="str">
         <v>Ok</v>
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H72" t="str">
         <v>Ok</v>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H73" t="str">
         <v>Ok</v>
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H74" t="str">
         <v>Ok</v>
@@ -3234,7 +3234,7 @@
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H75" t="str">
         <v>Ok</v>
@@ -3272,7 +3272,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H76" t="str">
         <v>Ok</v>
@@ -3310,7 +3310,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v>Ok</v>
@@ -3348,7 +3348,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H78" t="str">
         <v>NONONO</v>
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H81" t="str">
         <v>Ok</v>
@@ -3500,7 +3500,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H82" t="str">
         <v>Ok</v>
@@ -3538,7 +3538,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H83" t="str">
         <v>Ok</v>
@@ -3576,7 +3576,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H84" t="str">
         <v>Ok</v>
@@ -3614,7 +3614,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H85" t="str">
         <v>Ok</v>
@@ -3652,7 +3652,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H86" t="str">
         <v>Ok</v>
@@ -3690,7 +3690,7 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H87" t="str">
         <v>Ok</v>
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H88" t="str">
         <v>Ok</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H89" t="str">
         <v>Ok</v>
@@ -3804,7 +3804,7 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H90" t="str">
         <v>Ok</v>
@@ -3842,7 +3842,7 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H91" t="str">
         <v>Ok</v>
@@ -3880,7 +3880,7 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H92" t="str">
         <v>Ok</v>
@@ -3918,7 +3918,7 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v>Ok</v>
@@ -3956,7 +3956,7 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H94" t="str">
         <v>Ok</v>
@@ -3994,7 +3994,7 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H95" t="str">
         <v>Ok</v>
@@ -4032,7 +4032,7 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H96" t="str">
         <v>Ok</v>
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H97" t="str">
         <v>Ok</v>
@@ -4108,7 +4108,7 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H98" t="str">
         <v>Ok</v>
@@ -4146,7 +4146,7 @@
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H99" t="str">
         <v>Ok</v>
@@ -4184,7 +4184,7 @@
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H100" t="str">
         <v>Ok</v>
@@ -4222,7 +4222,7 @@
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H101" t="str">
         <v>Ok</v>
@@ -4260,7 +4260,7 @@
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H102" t="str">
         <v>Ok</v>
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H103" t="str">
         <v>Ok</v>
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H104" t="str">
         <v>Ok</v>
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H105" t="str">
         <v>Ok</v>
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H106" t="str">
         <v>Ok</v>
@@ -4450,7 +4450,7 @@
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H107" t="str">
         <v>Ok</v>
@@ -4488,7 +4488,7 @@
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H108" t="str">
         <v>Ok</v>
@@ -4526,7 +4526,7 @@
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H109" t="str">
         <v>Ok</v>
@@ -4564,7 +4564,7 @@
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H110" t="str">
         <v>Ok</v>
@@ -4602,7 +4602,7 @@
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H111" t="str">
         <v>Ok</v>
@@ -4640,7 +4640,7 @@
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H112" t="str">
         <v>NONONO</v>
@@ -4678,7 +4678,7 @@
         <v/>
       </c>
       <c r="G113" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H113" t="str">
         <v>Ok</v>
@@ -4716,7 +4716,7 @@
         <v/>
       </c>
       <c r="G114" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H114" t="str">
         <v>Ok</v>
@@ -4754,7 +4754,7 @@
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H115" t="str">
         <v>Ok</v>
@@ -4792,7 +4792,7 @@
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H116" t="str">
         <v>Ok</v>
@@ -4830,7 +4830,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H117" t="str">
         <v>Ok</v>
@@ -4868,7 +4868,7 @@
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H118" t="str">
         <v>Ok</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="G119" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H119" t="str">
         <v>Ok</v>
@@ -4944,7 +4944,7 @@
         <v/>
       </c>
       <c r="G120" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H120" t="str">
         <v>Ok</v>
@@ -4982,7 +4982,7 @@
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H121" t="str">
         <v>Ok</v>
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H122" t="str">
         <v>Ok</v>
@@ -5058,7 +5058,7 @@
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H123" t="str">
         <v>Ok</v>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H124" t="str">
         <v>Ok</v>
@@ -5134,7 +5134,7 @@
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H125" t="str">
         <v>Ok</v>
@@ -5172,7 +5172,7 @@
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H126" t="str">
         <v>Ok</v>
@@ -5210,7 +5210,7 @@
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H127" t="str">
         <v>Ok</v>
@@ -5248,7 +5248,7 @@
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H128" t="str">
         <v>Ok</v>
@@ -5286,7 +5286,7 @@
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H129" t="str">
         <v>Ok</v>
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H130" t="str">
         <v>Ok</v>
@@ -5362,7 +5362,7 @@
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H131" t="str">
         <v>Ok</v>
@@ -5400,7 +5400,7 @@
         <v/>
       </c>
       <c r="G132" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H132" t="str">
         <v>Ok</v>
@@ -5438,7 +5438,7 @@
         <v/>
       </c>
       <c r="G133" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H133" t="str">
         <v>Ok</v>
@@ -5476,7 +5476,7 @@
         <v/>
       </c>
       <c r="G134" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H134" t="str">
         <v>Ok</v>
@@ -5552,7 +5552,7 @@
         <v/>
       </c>
       <c r="G136" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H136" t="str">
         <v>Ok</v>
@@ -5590,7 +5590,7 @@
         <v/>
       </c>
       <c r="G137" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H137" t="str">
         <v>Ok</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="G138" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H138" t="str">
         <v>Ok</v>
@@ -5666,7 +5666,7 @@
         <v/>
       </c>
       <c r="G139" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H139" t="str">
         <v>Ok</v>
@@ -5704,7 +5704,7 @@
         <v/>
       </c>
       <c r="G140" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H140" t="str">
         <v>Ok</v>
@@ -5742,7 +5742,7 @@
         <v/>
       </c>
       <c r="G141" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H141" t="str">
         <v>Ok</v>
@@ -5780,7 +5780,7 @@
         <v/>
       </c>
       <c r="G142" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H142" t="str">
         <v>Ok</v>
@@ -5818,7 +5818,7 @@
         <v/>
       </c>
       <c r="G143" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H143" t="str">
         <v>Ok</v>
@@ -5856,7 +5856,7 @@
         <v/>
       </c>
       <c r="G144" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H144" t="str">
         <v>NONONO</v>
@@ -5894,7 +5894,7 @@
         <v/>
       </c>
       <c r="G145" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H145" t="str">
         <v>Ok</v>
@@ -5932,7 +5932,7 @@
         <v/>
       </c>
       <c r="G146" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H146" t="str">
         <v>Ok</v>
@@ -5970,7 +5970,7 @@
         <v/>
       </c>
       <c r="G147" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H147" t="str">
         <v>Ok</v>
@@ -6008,7 +6008,7 @@
         <v/>
       </c>
       <c r="G148" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H148" t="str">
         <v>Ok</v>
@@ -6046,7 +6046,7 @@
         <v/>
       </c>
       <c r="G149" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H149" t="str">
         <v>Ok</v>
@@ -6084,7 +6084,7 @@
         <v/>
       </c>
       <c r="G150" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H150" t="str">
         <v>Ok</v>
@@ -6122,7 +6122,7 @@
         <v/>
       </c>
       <c r="G151" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H151" t="str">
         <v>Ok</v>
@@ -6160,7 +6160,7 @@
         <v/>
       </c>
       <c r="G152" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H152" t="str">
         <v>Ok</v>
@@ -6198,7 +6198,7 @@
         <v/>
       </c>
       <c r="G153" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H153" t="str">
         <v>Ok</v>
@@ -6236,7 +6236,7 @@
         <v/>
       </c>
       <c r="G154" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H154" t="str">
         <v>Ok</v>
@@ -6274,7 +6274,7 @@
         <v/>
       </c>
       <c r="G155" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H155" t="str">
         <v>Ok</v>
@@ -6312,7 +6312,7 @@
         <v/>
       </c>
       <c r="G156" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H156" t="str">
         <v>Ok</v>
@@ -6350,7 +6350,7 @@
         <v/>
       </c>
       <c r="G157" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H157" t="str">
         <v>Ok</v>
@@ -6388,7 +6388,7 @@
         <v/>
       </c>
       <c r="G158" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H158" t="str">
         <v>Ok</v>
@@ -6426,7 +6426,7 @@
         <v/>
       </c>
       <c r="G159" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H159" t="str">
         <v>Ok</v>
@@ -6464,7 +6464,7 @@
         <v/>
       </c>
       <c r="G160" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H160" t="str">
         <v>Ok</v>
@@ -6502,7 +6502,7 @@
         <v/>
       </c>
       <c r="G161" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H161" t="str">
         <v>Ok</v>
@@ -6540,7 +6540,7 @@
         <v/>
       </c>
       <c r="G162" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H162" t="str">
         <v>Ok</v>
@@ -6578,7 +6578,7 @@
         <v/>
       </c>
       <c r="G163" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H163" t="str">
         <v>Ok</v>
@@ -6616,7 +6616,7 @@
         <v/>
       </c>
       <c r="G164" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H164" t="str">
         <v>Ok</v>
@@ -6654,7 +6654,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H165" t="str">
         <v>Ok</v>
@@ -6692,7 +6692,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H166" t="str">
         <v>Ok</v>
@@ -6730,7 +6730,7 @@
         <v/>
       </c>
       <c r="G167" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H167" t="str">
         <v>Ok</v>
@@ -6768,7 +6768,7 @@
         <v/>
       </c>
       <c r="G168" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H168" t="str">
         <v>Ok</v>
@@ -6806,7 +6806,7 @@
         <v/>
       </c>
       <c r="G169" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H169" t="str">
         <v>Ok</v>
@@ -6844,7 +6844,7 @@
         <v/>
       </c>
       <c r="G170" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H170" t="str">
         <v>Ok</v>
@@ -6882,7 +6882,7 @@
         <v/>
       </c>
       <c r="G171" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H171" t="str">
         <v>Ok</v>
@@ -6920,7 +6920,7 @@
         <v/>
       </c>
       <c r="G172" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H172" t="str">
         <v>NONONO</v>
@@ -6958,7 +6958,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H173" t="str">
         <v>Ok</v>
@@ -6996,7 +6996,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H174" t="str">
         <v>Ok</v>
@@ -7034,7 +7034,7 @@
         <v/>
       </c>
       <c r="G175" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H175" t="str">
         <v>Ok</v>
@@ -7072,7 +7072,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H176" t="str">
         <v>Ok</v>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="G177" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H177" t="str">
         <v>Ok</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="G178" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H178" t="str">
         <v>Ok</v>
@@ -7186,7 +7186,7 @@
         <v/>
       </c>
       <c r="G179" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H179" t="str">
         <v>Ok</v>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="G180" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H180" t="str">
         <v>Ok</v>
@@ -7262,7 +7262,7 @@
         <v/>
       </c>
       <c r="G181" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H181" t="str">
         <v>NONONO</v>
@@ -7300,7 +7300,7 @@
         <v/>
       </c>
       <c r="G182" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H182" t="str">
         <v>NONONO</v>
@@ -7338,7 +7338,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H183" t="str">
         <v>Ok</v>
@@ -7376,7 +7376,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H184" t="str">
         <v>Ok</v>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H185" t="str">
         <v>Ok</v>
@@ -7452,7 +7452,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H186" t="str">
         <v>NONONO</v>
@@ -7490,7 +7490,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H187" t="str">
         <v>Ok</v>
@@ -7528,7 +7528,7 @@
         <v/>
       </c>
       <c r="G188" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H188" t="str">
         <v>Ok</v>
@@ -7566,7 +7566,7 @@
         <v/>
       </c>
       <c r="G189" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H189" t="str">
         <v>Ok</v>
@@ -7604,7 +7604,7 @@
         <v/>
       </c>
       <c r="G190" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H190" t="str">
         <v>Ok</v>
@@ -7680,7 +7680,7 @@
         <v/>
       </c>
       <c r="G192" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H192" t="str">
         <v>Ok</v>
@@ -7718,7 +7718,7 @@
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H193" t="str">
         <v>Ok</v>
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="G194" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H194" t="str">
         <v>Ok</v>
@@ -7794,7 +7794,7 @@
         <v/>
       </c>
       <c r="G195" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H195" t="str">
         <v>Ok</v>
@@ -7832,7 +7832,7 @@
         <v/>
       </c>
       <c r="G196" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H196" t="str">
         <v>Ok</v>
@@ -7870,7 +7870,7 @@
         <v/>
       </c>
       <c r="G197" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H197" t="str">
         <v>Ok</v>
@@ -7908,7 +7908,7 @@
         <v/>
       </c>
       <c r="G198" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H198" t="str">
         <v>Ok</v>
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H199" t="str">
         <v>Ok</v>
@@ -7984,7 +7984,7 @@
         <v/>
       </c>
       <c r="G200" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H200" t="str">
         <v>Ok</v>
@@ -8022,7 +8022,7 @@
         <v/>
       </c>
       <c r="G201" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H201" t="str">
         <v>Ok</v>
@@ -8060,7 +8060,7 @@
         <v/>
       </c>
       <c r="G202" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H202" t="str">
         <v>Ok</v>
@@ -8098,7 +8098,7 @@
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H203" t="str">
         <v>Ok</v>
@@ -8136,7 +8136,7 @@
         <v/>
       </c>
       <c r="G204" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H204" t="str">
         <v>Ok</v>
@@ -8174,7 +8174,7 @@
         <v/>
       </c>
       <c r="G205" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H205" t="str">
         <v>Ok</v>
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="G206" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H206" t="str">
         <v>Ok</v>
@@ -8250,7 +8250,7 @@
         <v/>
       </c>
       <c r="G207" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H207" t="str">
         <v>Ok</v>
@@ -8288,7 +8288,7 @@
         <v/>
       </c>
       <c r="G208" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H208" t="str">
         <v>Ok</v>
@@ -8326,7 +8326,7 @@
         <v/>
       </c>
       <c r="G209" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H209" t="str">
         <v>Ok</v>
@@ -8364,7 +8364,7 @@
         <v/>
       </c>
       <c r="G210" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H210" t="str">
         <v>Ok</v>
@@ -8402,7 +8402,7 @@
         <v/>
       </c>
       <c r="G211" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H211" t="str">
         <v>Ok</v>
@@ -8440,7 +8440,7 @@
         <v/>
       </c>
       <c r="G212" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H212" t="str">
         <v>Ok</v>
@@ -8478,7 +8478,7 @@
         <v/>
       </c>
       <c r="G213" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H213" t="str">
         <v>Ok</v>
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="G214" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H214" t="str">
         <v>Ok</v>
@@ -8554,7 +8554,7 @@
         <v/>
       </c>
       <c r="G215" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H215" t="str">
         <v>Ok</v>
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H216" t="str">
         <v>Ok</v>
@@ -8630,7 +8630,7 @@
         <v/>
       </c>
       <c r="G217" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H217" t="str">
         <v>Ok</v>
@@ -8668,7 +8668,7 @@
         <v/>
       </c>
       <c r="G218" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H218" t="str">
         <v>Ok</v>
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="G219" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H219" t="str">
         <v>Ok</v>
@@ -8744,7 +8744,7 @@
         <v/>
       </c>
       <c r="G220" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H220" t="str">
         <v>Ok</v>
@@ -8782,7 +8782,7 @@
         <v/>
       </c>
       <c r="G221" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H221" t="str">
         <v>Ok</v>
@@ -8820,7 +8820,7 @@
         <v/>
       </c>
       <c r="G222" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H222" t="str">
         <v>Ok</v>
@@ -8858,7 +8858,7 @@
         <v/>
       </c>
       <c r="G223" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H223" t="str">
         <v>Ok</v>
@@ -8896,7 +8896,7 @@
         <v/>
       </c>
       <c r="G224" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H224" t="str">
         <v>Ok</v>
@@ -8934,7 +8934,7 @@
         <v/>
       </c>
       <c r="G225" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H225" t="str">
         <v>Ok</v>
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="G226" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H226" t="str">
         <v>Ok</v>
@@ -9010,7 +9010,7 @@
         <v/>
       </c>
       <c r="G227" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H227" t="str">
         <v>Ok</v>
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H228" t="str">
         <v>Ok</v>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="G229" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H229" t="str">
         <v>Ok</v>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="G230" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H230" t="str">
         <v>Ok</v>
@@ -9162,7 +9162,7 @@
         <v/>
       </c>
       <c r="G231" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H231" t="str">
         <v>Ok</v>
@@ -9200,7 +9200,7 @@
         <v/>
       </c>
       <c r="G232" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H232" t="str">
         <v>Ok</v>
@@ -9238,7 +9238,7 @@
         <v/>
       </c>
       <c r="G233" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H233" t="str">
         <v>Ok</v>
@@ -9276,7 +9276,7 @@
         <v/>
       </c>
       <c r="G234" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H234" t="str">
         <v>Ok</v>
@@ -9314,7 +9314,7 @@
         <v/>
       </c>
       <c r="G235" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H235" t="str">
         <v>Ok</v>
@@ -9352,7 +9352,7 @@
         <v/>
       </c>
       <c r="G236" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H236" t="str">
         <v>Ok</v>
@@ -9390,7 +9390,7 @@
         <v/>
       </c>
       <c r="G237" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H237" t="str">
         <v>Ok</v>
@@ -9428,7 +9428,7 @@
         <v/>
       </c>
       <c r="G238" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H238" t="str">
         <v>Ok</v>
@@ -9466,7 +9466,7 @@
         <v/>
       </c>
       <c r="G239" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H239" t="str">
         <v>Ok</v>
@@ -9504,7 +9504,7 @@
         <v/>
       </c>
       <c r="G240" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H240" t="str">
         <v>Ok</v>
@@ -9542,7 +9542,7 @@
         <v/>
       </c>
       <c r="G241" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H241" t="str">
         <v>Ok</v>
@@ -9580,7 +9580,7 @@
         <v/>
       </c>
       <c r="G242" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H242" t="str">
         <v>Ok</v>
@@ -9618,7 +9618,7 @@
         <v/>
       </c>
       <c r="G243" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H243" t="str">
         <v>Ok</v>
@@ -9656,7 +9656,7 @@
         <v/>
       </c>
       <c r="G244" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H244" t="str">
         <v>Ok</v>
@@ -9694,7 +9694,7 @@
         <v/>
       </c>
       <c r="G245" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H245" t="str">
         <v>Ok</v>
@@ -9732,7 +9732,7 @@
         <v/>
       </c>
       <c r="G246" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H246" t="str">
         <v>Ok</v>
@@ -9770,7 +9770,7 @@
         <v/>
       </c>
       <c r="G247" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H247" t="str">
         <v>Ok</v>
@@ -9808,7 +9808,7 @@
         <v/>
       </c>
       <c r="G248" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H248" t="str">
         <v>Ok</v>
@@ -9846,7 +9846,7 @@
         <v/>
       </c>
       <c r="G249" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H249" t="str">
         <v>Ok</v>
@@ -9884,7 +9884,7 @@
         <v/>
       </c>
       <c r="G250" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H250" t="str">
         <v>Ok</v>
@@ -9922,7 +9922,7 @@
         <v/>
       </c>
       <c r="G251" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H251" t="str">
         <v>Ok</v>
@@ -9960,7 +9960,7 @@
         <v/>
       </c>
       <c r="G252" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H252" t="str">
         <v>Ok</v>
@@ -9998,7 +9998,7 @@
         <v/>
       </c>
       <c r="G253" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H253" t="str">
         <v>Ok</v>
@@ -10036,7 +10036,7 @@
         <v/>
       </c>
       <c r="G254" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H254" t="str">
         <v>Ok</v>
@@ -10074,7 +10074,7 @@
         <v/>
       </c>
       <c r="G255" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H255" t="str">
         <v>Ok</v>
@@ -10112,7 +10112,7 @@
         <v/>
       </c>
       <c r="G256" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H256" t="str">
         <v>Ok</v>
@@ -10150,7 +10150,7 @@
         <v/>
       </c>
       <c r="G257" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H257" t="str">
         <v>Ok</v>
@@ -10188,7 +10188,7 @@
         <v/>
       </c>
       <c r="G258" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H258" t="str">
         <v>Ok</v>
@@ -10226,7 +10226,7 @@
         <v/>
       </c>
       <c r="G259" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H259" t="str">
         <v>Ok</v>
@@ -10264,7 +10264,7 @@
         <v/>
       </c>
       <c r="G260" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H260" t="str">
         <v>Ok</v>
@@ -10302,7 +10302,7 @@
         <v/>
       </c>
       <c r="G261" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H261" t="str">
         <v>Ok</v>
@@ -10340,7 +10340,7 @@
         <v/>
       </c>
       <c r="G262" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H262" t="str">
         <v>Ok</v>
@@ -10378,7 +10378,7 @@
         <v/>
       </c>
       <c r="G263" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H263" t="str">
         <v>Ok</v>
@@ -10416,7 +10416,7 @@
         <v/>
       </c>
       <c r="G264" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H264" t="str">
         <v>Ok</v>
@@ -10454,7 +10454,7 @@
         <v/>
       </c>
       <c r="G265" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H265" t="str">
         <v>Ok</v>
@@ -10492,7 +10492,7 @@
         <v/>
       </c>
       <c r="G266" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H266" t="str">
         <v>Ok</v>
@@ -10530,7 +10530,7 @@
         <v/>
       </c>
       <c r="G267" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H267" t="str">
         <v>Ok</v>
@@ -10568,7 +10568,7 @@
         <v/>
       </c>
       <c r="G268" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H268" t="str">
         <v>Ok</v>
@@ -10606,7 +10606,7 @@
         <v/>
       </c>
       <c r="G269" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H269" t="str">
         <v>Ok</v>
@@ -10644,7 +10644,7 @@
         <v/>
       </c>
       <c r="G270" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H270" t="str">
         <v>Ok</v>
@@ -10682,7 +10682,7 @@
         <v/>
       </c>
       <c r="G271" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H271" t="str">
         <v>Ok</v>
@@ -10720,7 +10720,7 @@
         <v/>
       </c>
       <c r="G272" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H272" t="str">
         <v>Ok</v>
@@ -10834,7 +10834,7 @@
         <v/>
       </c>
       <c r="G275" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H275" t="str">
         <v>Ok</v>
@@ -10872,7 +10872,7 @@
         <v/>
       </c>
       <c r="G276" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H276" t="str">
         <v>Ok</v>
@@ -10910,7 +10910,7 @@
         <v/>
       </c>
       <c r="G277" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H277" t="str">
         <v>Ok</v>
@@ -10948,7 +10948,7 @@
         <v/>
       </c>
       <c r="G278" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H278" t="str">
         <v>Ok</v>
@@ -10986,7 +10986,7 @@
         <v/>
       </c>
       <c r="G279" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H279" t="str">
         <v>Ok</v>
@@ -11024,7 +11024,7 @@
         <v/>
       </c>
       <c r="G280" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H280" t="str">
         <v>Ok</v>
@@ -11062,7 +11062,7 @@
         <v/>
       </c>
       <c r="G281" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H281" t="str">
         <v>Ok</v>
@@ -11100,7 +11100,7 @@
         <v/>
       </c>
       <c r="G282" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H282" t="str">
         <v>Ok</v>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="G283" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H283" t="str">
         <v>Ok</v>
@@ -11176,7 +11176,7 @@
         <v/>
       </c>
       <c r="G284" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H284" t="str">
         <v>Ok</v>
@@ -11214,7 +11214,7 @@
         <v/>
       </c>
       <c r="G285" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H285" t="str">
         <v>Ok</v>
@@ -11252,7 +11252,7 @@
         <v/>
       </c>
       <c r="G286" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H286" t="str">
         <v>Ok</v>
@@ -11290,7 +11290,7 @@
         <v/>
       </c>
       <c r="G287" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H287" t="str">
         <v>Ok</v>
@@ -11328,7 +11328,7 @@
         <v/>
       </c>
       <c r="G288" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H288" t="str">
         <v>Ok</v>
@@ -11366,7 +11366,7 @@
         <v/>
       </c>
       <c r="G289" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H289" t="str">
         <v>Ok</v>
@@ -11404,7 +11404,7 @@
         <v/>
       </c>
       <c r="G290" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H290" t="str">
         <v>Ok</v>
@@ -11442,7 +11442,7 @@
         <v/>
       </c>
       <c r="G291" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H291" t="str">
         <v>Ok</v>
@@ -11480,7 +11480,7 @@
         <v/>
       </c>
       <c r="G292" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H292" t="str">
         <v>Ok</v>
@@ -11518,7 +11518,7 @@
         <v/>
       </c>
       <c r="G293" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H293" t="str">
         <v>Ok</v>
@@ -11556,7 +11556,7 @@
         <v/>
       </c>
       <c r="G294" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H294" t="str">
         <v>Ok</v>
@@ -11594,7 +11594,7 @@
         <v/>
       </c>
       <c r="G295" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H295" t="str">
         <v>Ok</v>
@@ -11632,7 +11632,7 @@
         <v/>
       </c>
       <c r="G296" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H296" t="str">
         <v>Ok</v>
@@ -11670,7 +11670,7 @@
         <v/>
       </c>
       <c r="G297" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H297" t="str">
         <v>Ok</v>
@@ -11708,7 +11708,7 @@
         <v/>
       </c>
       <c r="G298" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H298" t="str">
         <v>Ok</v>
@@ -11746,7 +11746,7 @@
         <v/>
       </c>
       <c r="G299" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H299" t="str">
         <v>Ok</v>
@@ -11784,7 +11784,7 @@
         <v/>
       </c>
       <c r="G300" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H300" t="str">
         <v>NONONO</v>
@@ -11822,7 +11822,7 @@
         <v/>
       </c>
       <c r="G301" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H301" t="str">
         <v>Ok</v>
@@ -11860,7 +11860,7 @@
         <v/>
       </c>
       <c r="G302" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H302" t="str">
         <v>Ok</v>
@@ -11898,7 +11898,7 @@
         <v/>
       </c>
       <c r="G303" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H303" t="str">
         <v>Ok</v>
@@ -11936,7 +11936,7 @@
         <v/>
       </c>
       <c r="G304" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H304" t="str">
         <v>Ok</v>
@@ -11974,7 +11974,7 @@
         <v/>
       </c>
       <c r="G305" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H305" t="str">
         <v>Ok</v>
@@ -12012,7 +12012,7 @@
         <v/>
       </c>
       <c r="G306" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H306" t="str">
         <v>NONONO</v>
@@ -12050,7 +12050,7 @@
         <v/>
       </c>
       <c r="G307" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H307" t="str">
         <v>NONONO</v>
@@ -12088,7 +12088,7 @@
         <v/>
       </c>
       <c r="G308" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H308" t="str">
         <v>Ok</v>
@@ -12126,7 +12126,7 @@
         <v/>
       </c>
       <c r="G309" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H309" t="str">
         <v>Ok</v>
@@ -12164,7 +12164,7 @@
         <v/>
       </c>
       <c r="G310" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H310" t="str">
         <v>Ok</v>
@@ -12202,7 +12202,7 @@
         <v/>
       </c>
       <c r="G311" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H311" t="str">
         <v>Ok</v>
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="G312" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H312" t="str">
         <v>NONONO</v>
@@ -12278,7 +12278,7 @@
         <v/>
       </c>
       <c r="G313" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H313" t="str">
         <v>Ok</v>
@@ -12316,7 +12316,7 @@
         <v/>
       </c>
       <c r="G314" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H314" t="str">
         <v>NONONO</v>
@@ -12354,7 +12354,7 @@
         <v/>
       </c>
       <c r="G315" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H315" t="str">
         <v>Ok</v>
@@ -12392,7 +12392,7 @@
         <v/>
       </c>
       <c r="G316" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H316" t="str">
         <v>Ok</v>
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="G317" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H317" t="str">
         <v>Ok</v>
@@ -12468,7 +12468,7 @@
         <v/>
       </c>
       <c r="G318" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H318" t="str">
         <v>NONONO</v>
@@ -12506,7 +12506,7 @@
         <v/>
       </c>
       <c r="G319" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H319" t="str">
         <v>Ok</v>
@@ -12544,7 +12544,7 @@
         <v/>
       </c>
       <c r="G320" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H320" t="str">
         <v>NONONO</v>
@@ -12582,7 +12582,7 @@
         <v/>
       </c>
       <c r="G321" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H321" t="str">
         <v>NONONO</v>
@@ -12620,7 +12620,7 @@
         <v/>
       </c>
       <c r="G322" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H322" t="str">
         <v>NONONO</v>
@@ -12658,7 +12658,7 @@
         <v/>
       </c>
       <c r="G323" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H323" t="str">
         <v>Ok</v>
@@ -12696,7 +12696,7 @@
         <v/>
       </c>
       <c r="G324" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H324" t="str">
         <v>Ok</v>
@@ -12734,7 +12734,7 @@
         <v/>
       </c>
       <c r="G325" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H325" t="str">
         <v>Ok</v>
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="G326" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H326" t="str">
         <v>NONONO</v>
@@ -12810,7 +12810,7 @@
         <v/>
       </c>
       <c r="G327" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H327" t="str">
         <v>Ok</v>
@@ -13000,7 +13000,7 @@
         <v/>
       </c>
       <c r="G332" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H332" t="str">
         <v>NONONO</v>
@@ -13038,7 +13038,7 @@
         <v/>
       </c>
       <c r="G333" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H333" t="str">
         <v>Ok</v>
@@ -13076,7 +13076,7 @@
         <v/>
       </c>
       <c r="G334" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H334" t="str">
         <v>Ok</v>
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="G335" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H335" t="str">
         <v>NONONO</v>
@@ -13152,7 +13152,7 @@
         <v/>
       </c>
       <c r="G336" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H336" t="str">
         <v>NONONO</v>
@@ -13190,7 +13190,7 @@
         <v/>
       </c>
       <c r="G337" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H337" t="str">
         <v>NONONO</v>
@@ -13228,7 +13228,7 @@
         <v/>
       </c>
       <c r="G338" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H338" t="str">
         <v>Ok</v>
@@ -13266,7 +13266,7 @@
         <v/>
       </c>
       <c r="G339" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H339" t="str">
         <v>Ok</v>
@@ -13304,7 +13304,7 @@
         <v/>
       </c>
       <c r="G340" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H340" t="str">
         <v>NONONO</v>
@@ -13342,7 +13342,7 @@
         <v/>
       </c>
       <c r="G341" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H341" t="str">
         <v>NONONO</v>
@@ -13380,7 +13380,7 @@
         <v/>
       </c>
       <c r="G342" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H342" t="str">
         <v>Ok</v>
@@ -13418,7 +13418,7 @@
         <v/>
       </c>
       <c r="G343" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H343" t="str">
         <v>Ok</v>
@@ -13456,7 +13456,7 @@
         <v/>
       </c>
       <c r="G344" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H344" t="str">
         <v>Ok</v>
@@ -13494,7 +13494,7 @@
         <v/>
       </c>
       <c r="G345" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H345" t="str">
         <v>Ok</v>
@@ -13532,7 +13532,7 @@
         <v/>
       </c>
       <c r="G346" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H346" t="str">
         <v>Ok</v>
@@ -13570,7 +13570,7 @@
         <v/>
       </c>
       <c r="G347" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H347" t="str">
         <v>Ok</v>
@@ -13608,7 +13608,7 @@
         <v/>
       </c>
       <c r="G348" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H348" t="str">
         <v>Ok</v>
@@ -13646,7 +13646,7 @@
         <v/>
       </c>
       <c r="G349" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H349" t="str">
         <v>NONONO</v>
@@ -13684,7 +13684,7 @@
         <v/>
       </c>
       <c r="G350" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H350" t="str">
         <v>Ok</v>
@@ -13722,7 +13722,7 @@
         <v/>
       </c>
       <c r="G351" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H351" t="str">
         <v>NONONO</v>
@@ -13760,7 +13760,7 @@
         <v/>
       </c>
       <c r="G352" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H352" t="str">
         <v>Ok</v>
@@ -13836,7 +13836,7 @@
         <v/>
       </c>
       <c r="G354" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H354" t="str">
         <v>NONONO</v>
@@ -13874,7 +13874,7 @@
         <v/>
       </c>
       <c r="G355" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H355" t="str">
         <v>NONONO</v>
@@ -13912,7 +13912,7 @@
         <v/>
       </c>
       <c r="G356" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H356" t="str">
         <v>NONONO</v>
@@ -13950,7 +13950,7 @@
         <v/>
       </c>
       <c r="G357" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H357" t="str">
         <v>NONONO</v>
@@ -13988,7 +13988,7 @@
         <v/>
       </c>
       <c r="G358" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H358" t="str">
         <v>NONONO</v>
@@ -14026,7 +14026,7 @@
         <v/>
       </c>
       <c r="G359" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H359" t="str">
         <v>Ok</v>
@@ -14064,7 +14064,7 @@
         <v/>
       </c>
       <c r="G360" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H360" t="str">
         <v>NONONO</v>
@@ -14102,7 +14102,7 @@
         <v/>
       </c>
       <c r="G361" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H361" t="str">
         <v>Ok</v>
@@ -14140,7 +14140,7 @@
         <v/>
       </c>
       <c r="G362" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H362" t="str">
         <v>Ok</v>
@@ -14178,7 +14178,7 @@
         <v/>
       </c>
       <c r="G363" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H363" t="str">
         <v>Ok</v>
@@ -14216,7 +14216,7 @@
         <v/>
       </c>
       <c r="G364" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H364" t="str">
         <v>NONONO</v>
@@ -14254,7 +14254,7 @@
         <v/>
       </c>
       <c r="G365" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H365" t="str">
         <v>NONONO</v>
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
       <c r="G366" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H366" t="str">
         <v>NONONO</v>
@@ -14330,7 +14330,7 @@
         <v/>
       </c>
       <c r="G367" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H367" t="str">
         <v>NONONO</v>
@@ -14368,7 +14368,7 @@
         <v/>
       </c>
       <c r="G368" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H368" t="str">
         <v>NONONO</v>
@@ -14406,7 +14406,7 @@
         <v/>
       </c>
       <c r="G369" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H369" t="str">
         <v>Ok</v>
@@ -14444,7 +14444,7 @@
         <v/>
       </c>
       <c r="G370" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H370" t="str">
         <v>NONONO</v>
@@ -14482,7 +14482,7 @@
         <v/>
       </c>
       <c r="G371" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H371" t="str">
         <v>NONONO</v>
@@ -14520,7 +14520,7 @@
         <v/>
       </c>
       <c r="G372" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H372" t="str">
         <v>Ok</v>
@@ -14558,7 +14558,7 @@
         <v/>
       </c>
       <c r="G373" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H373" t="str">
         <v>NONONO</v>
@@ -14596,7 +14596,7 @@
         <v/>
       </c>
       <c r="G374" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H374" t="str">
         <v>NONONO</v>
@@ -14634,7 +14634,7 @@
         <v/>
       </c>
       <c r="G375" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H375" t="str">
         <v>Ok</v>
@@ -14672,7 +14672,7 @@
         <v/>
       </c>
       <c r="G376" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H376" t="str">
         <v>NONONO</v>
@@ -14710,7 +14710,7 @@
         <v/>
       </c>
       <c r="G377" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H377" t="str">
         <v>NONONO</v>
@@ -14748,7 +14748,7 @@
         <v/>
       </c>
       <c r="G378" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H378" t="str">
         <v>NONONO</v>
@@ -14786,7 +14786,7 @@
         <v/>
       </c>
       <c r="G379" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H379" t="str">
         <v>NONONO</v>
@@ -14824,7 +14824,7 @@
         <v/>
       </c>
       <c r="G380" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H380" t="str">
         <v>NONONO</v>
@@ -14862,7 +14862,7 @@
         <v/>
       </c>
       <c r="G381" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H381" t="str">
         <v>NONONO</v>
@@ -14900,7 +14900,7 @@
         <v/>
       </c>
       <c r="G382" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H382" t="str">
         <v>NONONO</v>
@@ -14938,7 +14938,7 @@
         <v/>
       </c>
       <c r="G383" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H383" t="str">
         <v>NONONO</v>
@@ -14976,7 +14976,7 @@
         <v/>
       </c>
       <c r="G384" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H384" t="str">
         <v>NONONO</v>
@@ -15014,7 +15014,7 @@
         <v/>
       </c>
       <c r="G385" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H385" t="str">
         <v>NONONO</v>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
       <c r="G386" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H386" t="str">
         <v>NONONO</v>
@@ -15090,7 +15090,7 @@
         <v/>
       </c>
       <c r="G387" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H387" t="str">
         <v>NONONO</v>
@@ -15128,7 +15128,7 @@
         <v/>
       </c>
       <c r="G388" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H388" t="str">
         <v>NONONO</v>
@@ -15166,7 +15166,7 @@
         <v/>
       </c>
       <c r="G389" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H389" t="str">
         <v>NONONO</v>
@@ -15204,7 +15204,7 @@
         <v/>
       </c>
       <c r="G390" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H390" t="str">
         <v>NONONO</v>
@@ -15242,7 +15242,7 @@
         <v/>
       </c>
       <c r="G391" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H391" t="str">
         <v>NONONO</v>
@@ -15280,7 +15280,7 @@
         <v/>
       </c>
       <c r="G392" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H392" t="str">
         <v>NONONO</v>
@@ -15318,7 +15318,7 @@
         <v/>
       </c>
       <c r="G393" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H393" t="str">
         <v>Ok</v>
@@ -15356,7 +15356,7 @@
         <v/>
       </c>
       <c r="G394" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H394" t="str">
         <v>Ok</v>
@@ -15394,7 +15394,7 @@
         <v/>
       </c>
       <c r="G395" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H395" t="str">
         <v>NONONO</v>
@@ -15432,7 +15432,7 @@
         <v/>
       </c>
       <c r="G396" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H396" t="str">
         <v>Ok</v>
@@ -15470,7 +15470,7 @@
         <v/>
       </c>
       <c r="G397" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H397" t="str">
         <v>NONONO</v>
@@ -15508,7 +15508,7 @@
         <v/>
       </c>
       <c r="G398" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H398" t="str">
         <v>Ok</v>
@@ -15546,7 +15546,7 @@
         <v/>
       </c>
       <c r="G399" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H399" t="str">
         <v>NONONO</v>
@@ -15584,7 +15584,7 @@
         <v/>
       </c>
       <c r="G400" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H400" t="str">
         <v>NONONO</v>
@@ -15622,7 +15622,7 @@
         <v/>
       </c>
       <c r="G401" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H401" t="str">
         <v>Ok</v>
@@ -15660,7 +15660,7 @@
         <v/>
       </c>
       <c r="G402" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H402" t="str">
         <v>NONONO</v>
@@ -15698,7 +15698,7 @@
         <v/>
       </c>
       <c r="G403" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H403" t="str">
         <v>Ok</v>
@@ -15736,7 +15736,7 @@
         <v/>
       </c>
       <c r="G404" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H404" t="str">
         <v>NONONO</v>
@@ -15774,7 +15774,7 @@
         <v/>
       </c>
       <c r="G405" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H405" t="str">
         <v>NONONO</v>
@@ -15812,7 +15812,7 @@
         <v/>
       </c>
       <c r="G406" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H406" t="str">
         <v>NONONO</v>
@@ -15850,7 +15850,7 @@
         <v/>
       </c>
       <c r="G407" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H407" t="str">
         <v>Ok</v>
@@ -15888,7 +15888,7 @@
         <v/>
       </c>
       <c r="G408" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H408" t="str">
         <v>Ok</v>
@@ -15926,7 +15926,7 @@
         <v/>
       </c>
       <c r="G409" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H409" t="str">
         <v>NONONO</v>
@@ -15964,7 +15964,7 @@
         <v/>
       </c>
       <c r="G410" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H410" t="str">
         <v>Ok</v>
@@ -16002,7 +16002,7 @@
         <v/>
       </c>
       <c r="G411" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H411" t="str">
         <v>Ok</v>
@@ -16040,7 +16040,7 @@
         <v/>
       </c>
       <c r="G412" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H412" t="str">
         <v>NONONO</v>
@@ -16078,7 +16078,7 @@
         <v/>
       </c>
       <c r="G413" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H413" t="str">
         <v>Ok</v>
@@ -16116,7 +16116,7 @@
         <v/>
       </c>
       <c r="G414" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H414" t="str">
         <v>Ok</v>
@@ -16154,7 +16154,7 @@
         <v/>
       </c>
       <c r="G415" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H415" t="str">
         <v>Ok</v>
@@ -16192,7 +16192,7 @@
         <v/>
       </c>
       <c r="G416" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H416" t="str">
         <v>Ok</v>
@@ -16230,7 +16230,7 @@
         <v/>
       </c>
       <c r="G417" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H417" t="str">
         <v>Ok</v>
@@ -16268,7 +16268,7 @@
         <v/>
       </c>
       <c r="G418" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H418" t="str">
         <v>Ok</v>
@@ -16306,7 +16306,7 @@
         <v/>
       </c>
       <c r="G419" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H419" t="str">
         <v>Ok</v>
@@ -16344,7 +16344,7 @@
         <v/>
       </c>
       <c r="G420" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H420" t="str">
         <v>NONONO</v>
@@ -16382,7 +16382,7 @@
         <v/>
       </c>
       <c r="G421" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H421" t="str">
         <v>Ok</v>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="G422" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H422" t="str">
         <v>Ok</v>
@@ -16458,7 +16458,7 @@
         <v/>
       </c>
       <c r="G423" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H423" t="str">
         <v>Ok</v>
@@ -16496,7 +16496,7 @@
         <v/>
       </c>
       <c r="G424" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H424" t="str">
         <v>Ok</v>
@@ -16534,7 +16534,7 @@
         <v/>
       </c>
       <c r="G425" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H425" t="str">
         <v>Ok</v>
@@ -16572,7 +16572,7 @@
         <v/>
       </c>
       <c r="G426" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H426" t="str">
         <v>Ok</v>
@@ -16610,7 +16610,7 @@
         <v/>
       </c>
       <c r="G427" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H427" t="str">
         <v>NONONO</v>
@@ -16648,7 +16648,7 @@
         <v/>
       </c>
       <c r="G428" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H428" t="str">
         <v>NONONO</v>
@@ -16686,7 +16686,7 @@
         <v/>
       </c>
       <c r="G429" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H429" t="str">
         <v>Ok</v>
@@ -16724,7 +16724,7 @@
         <v/>
       </c>
       <c r="G430" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H430" t="str">
         <v>NONONO</v>
@@ -16762,7 +16762,7 @@
         <v/>
       </c>
       <c r="G431" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H431" t="str">
         <v>NONONO</v>
@@ -16800,7 +16800,7 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H432" t="str">
         <v>NONONO</v>
@@ -16838,7 +16838,7 @@
         <v/>
       </c>
       <c r="G433" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H433" t="str">
         <v>Ok</v>
@@ -16876,7 +16876,7 @@
         <v/>
       </c>
       <c r="G434" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H434" t="str">
         <v>NONONO</v>
@@ -16914,7 +16914,7 @@
         <v/>
       </c>
       <c r="G435" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H435" t="str">
         <v>Ok</v>
@@ -16952,7 +16952,7 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H436" t="str">
         <v>NONONO</v>
@@ -16990,7 +16990,7 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H437" t="str">
         <v>NONONO</v>
@@ -17028,7 +17028,7 @@
         <v/>
       </c>
       <c r="G438" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H438" t="str">
         <v>NONONO</v>
@@ -17066,7 +17066,7 @@
         <v/>
       </c>
       <c r="G439" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H439" t="str">
         <v>NONONO</v>
@@ -17104,7 +17104,7 @@
         <v/>
       </c>
       <c r="G440" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H440" t="str">
         <v>NONONO</v>
@@ -17142,7 +17142,7 @@
         <v/>
       </c>
       <c r="G441" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H441" t="str">
         <v>NONONO</v>
@@ -17180,7 +17180,7 @@
         <v/>
       </c>
       <c r="G442" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H442" t="str">
         <v>NONONO</v>
@@ -17218,7 +17218,7 @@
         <v/>
       </c>
       <c r="G443" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H443" t="str">
         <v>Ok</v>
@@ -17256,7 +17256,7 @@
         <v/>
       </c>
       <c r="G444" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H444" t="str">
         <v>NONONO</v>
@@ -17294,7 +17294,7 @@
         <v/>
       </c>
       <c r="G445" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H445" t="str">
         <v>Ok</v>
@@ -17332,7 +17332,7 @@
         <v/>
       </c>
       <c r="G446" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H446" t="str">
         <v>NONONO</v>
@@ -17370,7 +17370,7 @@
         <v/>
       </c>
       <c r="G447" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H447" t="str">
         <v>Ok</v>
@@ -17408,7 +17408,7 @@
         <v/>
       </c>
       <c r="G448" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H448" t="str">
         <v>Ok</v>
@@ -17446,7 +17446,7 @@
         <v/>
       </c>
       <c r="G449" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H449" t="str">
         <v>Ok</v>
@@ -17484,7 +17484,7 @@
         <v/>
       </c>
       <c r="G450" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H450" t="str">
         <v>Ok</v>
@@ -17522,7 +17522,7 @@
         <v/>
       </c>
       <c r="G451" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H451" t="str">
         <v>Ok</v>
@@ -17560,7 +17560,7 @@
         <v/>
       </c>
       <c r="G452" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H452" t="str">
         <v>Ok</v>
@@ -17598,7 +17598,7 @@
         <v/>
       </c>
       <c r="G453" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H453" t="str">
         <v>NONONO</v>
@@ -17636,7 +17636,7 @@
         <v/>
       </c>
       <c r="G454" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H454" t="str">
         <v>Ok</v>
@@ -17674,7 +17674,7 @@
         <v/>
       </c>
       <c r="G455" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H455" t="str">
         <v>Ok</v>
@@ -17712,7 +17712,7 @@
         <v/>
       </c>
       <c r="G456" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H456" t="str">
         <v>Ok</v>
@@ -17750,7 +17750,7 @@
         <v/>
       </c>
       <c r="G457" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H457" t="str">
         <v>Ok</v>
@@ -17788,7 +17788,7 @@
         <v/>
       </c>
       <c r="G458" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H458" t="str">
         <v>Ok</v>
@@ -17826,7 +17826,7 @@
         <v/>
       </c>
       <c r="G459" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H459" t="str">
         <v>NONONO</v>
@@ -17864,7 +17864,7 @@
         <v/>
       </c>
       <c r="G460" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H460" t="str">
         <v>NONONO</v>
@@ -17902,7 +17902,7 @@
         <v/>
       </c>
       <c r="G461" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H461" t="str">
         <v>NONONO</v>
@@ -17940,7 +17940,7 @@
         <v/>
       </c>
       <c r="G462" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H462" t="str">
         <v>NONONO</v>
@@ -17978,7 +17978,7 @@
         <v/>
       </c>
       <c r="G463" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H463" t="str">
         <v>NONONO</v>
@@ -18016,7 +18016,7 @@
         <v/>
       </c>
       <c r="G464" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H464" t="str">
         <v>NONONO</v>
@@ -18054,7 +18054,7 @@
         <v/>
       </c>
       <c r="G465" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H465" t="str">
         <v>NONONO</v>
@@ -18092,7 +18092,7 @@
         <v/>
       </c>
       <c r="G466" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H466" t="str">
         <v>NONONO</v>
@@ -18130,7 +18130,7 @@
         <v/>
       </c>
       <c r="G467" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H467" t="str">
         <v>Ok</v>
@@ -18168,7 +18168,7 @@
         <v/>
       </c>
       <c r="G468" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H468" t="str">
         <v>Ok</v>
@@ -18206,7 +18206,7 @@
         <v/>
       </c>
       <c r="G469" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H469" t="str">
         <v>Ok</v>
@@ -18244,7 +18244,7 @@
         <v/>
       </c>
       <c r="G470" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H470" t="str">
         <v>Ok</v>
@@ -18282,7 +18282,7 @@
         <v/>
       </c>
       <c r="G471" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H471" t="str">
         <v>Ok</v>
@@ -18320,7 +18320,7 @@
         <v/>
       </c>
       <c r="G472" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H472" t="str">
         <v>NONONO</v>
@@ -18358,7 +18358,7 @@
         <v/>
       </c>
       <c r="G473" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H473" t="str">
         <v>NONONO</v>
@@ -18396,7 +18396,7 @@
         <v/>
       </c>
       <c r="G474" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H474" t="str">
         <v>NONONO</v>
@@ -18434,7 +18434,7 @@
         <v/>
       </c>
       <c r="G475" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H475" t="str">
         <v>Ok</v>
@@ -18472,7 +18472,7 @@
         <v/>
       </c>
       <c r="G476" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H476" t="str">
         <v>Ok</v>
@@ -18510,7 +18510,7 @@
         <v/>
       </c>
       <c r="G477" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H477" t="str">
         <v>NONONO</v>
@@ -18548,7 +18548,7 @@
         <v/>
       </c>
       <c r="G478" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H478" t="str">
         <v>Ok</v>
@@ -18586,7 +18586,7 @@
         <v/>
       </c>
       <c r="G479" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H479" t="str">
         <v>Ok</v>
@@ -18624,7 +18624,7 @@
         <v/>
       </c>
       <c r="G480" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H480" t="str">
         <v>Ok</v>
@@ -18662,7 +18662,7 @@
         <v/>
       </c>
       <c r="G481" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H481" t="str">
         <v>Ok</v>
@@ -18700,7 +18700,7 @@
         <v/>
       </c>
       <c r="G482" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H482" t="str">
         <v>NONONO</v>
@@ -18738,7 +18738,7 @@
         <v/>
       </c>
       <c r="G483" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H483" t="str">
         <v>NONONO</v>
@@ -18776,7 +18776,7 @@
         <v/>
       </c>
       <c r="G484" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H484" t="str">
         <v>Ok</v>
@@ -18814,7 +18814,7 @@
         <v/>
       </c>
       <c r="G485" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H485" t="str">
         <v>Ok</v>
@@ -18852,7 +18852,7 @@
         <v/>
       </c>
       <c r="G486" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H486" t="str">
         <v>NONONO</v>
@@ -18890,7 +18890,7 @@
         <v/>
       </c>
       <c r="G487" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H487" t="str">
         <v>NONONO</v>
@@ -18928,7 +18928,7 @@
         <v/>
       </c>
       <c r="G488" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H488" t="str">
         <v>NONONO</v>
@@ -18966,7 +18966,7 @@
         <v/>
       </c>
       <c r="G489" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H489" t="str">
         <v>Ok</v>
@@ -19004,7 +19004,7 @@
         <v/>
       </c>
       <c r="G490" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H490" t="str">
         <v>NONONO</v>
@@ -19042,7 +19042,7 @@
         <v/>
       </c>
       <c r="G491" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H491" t="str">
         <v>Ok</v>
@@ -19080,7 +19080,7 @@
         <v/>
       </c>
       <c r="G492" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H492" t="str">
         <v>Ok</v>
@@ -19118,7 +19118,7 @@
         <v/>
       </c>
       <c r="G493" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H493" t="str">
         <v>Ok</v>
@@ -19156,7 +19156,7 @@
         <v/>
       </c>
       <c r="G494" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H494" t="str">
         <v>NONONO</v>
@@ -19194,7 +19194,7 @@
         <v/>
       </c>
       <c r="G495" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H495" t="str">
         <v>NONONO</v>
@@ -19232,7 +19232,7 @@
         <v/>
       </c>
       <c r="G496" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H496" t="str">
         <v>NONONO</v>
@@ -19270,7 +19270,7 @@
         <v/>
       </c>
       <c r="G497" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H497" t="str">
         <v>NONONO</v>
@@ -19308,7 +19308,7 @@
         <v/>
       </c>
       <c r="G498" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H498" t="str">
         <v>NONONO</v>
@@ -19346,7 +19346,7 @@
         <v/>
       </c>
       <c r="G499" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H499" t="str">
         <v>Ok</v>
@@ -19384,7 +19384,7 @@
         <v/>
       </c>
       <c r="G500" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H500" t="str">
         <v>Ok</v>
@@ -19422,7 +19422,7 @@
         <v/>
       </c>
       <c r="G501" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H501" t="str">
         <v>Ok</v>
@@ -19460,7 +19460,7 @@
         <v/>
       </c>
       <c r="G502" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H502" t="str">
         <v>NONONO</v>
@@ -19498,7 +19498,7 @@
         <v/>
       </c>
       <c r="G503" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H503" t="str">
         <v>Ok</v>
@@ -19536,7 +19536,7 @@
         <v/>
       </c>
       <c r="G504" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H504" t="str">
         <v>Ok</v>
@@ -19574,7 +19574,7 @@
         <v/>
       </c>
       <c r="G505" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H505" t="str">
         <v>Ok</v>
@@ -19612,7 +19612,7 @@
         <v/>
       </c>
       <c r="G506" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H506" t="str">
         <v>Ok</v>
@@ -19650,7 +19650,7 @@
         <v/>
       </c>
       <c r="G507" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H507" t="str">
         <v>Ok</v>
@@ -19688,7 +19688,7 @@
         <v/>
       </c>
       <c r="G508" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H508" t="str">
         <v>NONONO</v>
@@ -19726,7 +19726,7 @@
         <v/>
       </c>
       <c r="G509" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H509" t="str">
         <v>NONONO</v>
@@ -19764,7 +19764,7 @@
         <v/>
       </c>
       <c r="G510" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H510" t="str">
         <v>Ok</v>
@@ -19802,7 +19802,7 @@
         <v/>
       </c>
       <c r="G511" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H511" t="str">
         <v>Ok</v>
@@ -19840,7 +19840,7 @@
         <v/>
       </c>
       <c r="G512" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H512" t="str">
         <v>NONONO</v>
@@ -19878,7 +19878,7 @@
         <v/>
       </c>
       <c r="G513" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H513" t="str">
         <v>Ok</v>
@@ -19916,7 +19916,7 @@
         <v/>
       </c>
       <c r="G514" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H514" t="str">
         <v>Ok</v>
@@ -19954,7 +19954,7 @@
         <v/>
       </c>
       <c r="G515" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H515" t="str">
         <v>Ok</v>
@@ -19992,7 +19992,7 @@
         <v/>
       </c>
       <c r="G516" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H516" t="str">
         <v>Ok</v>
@@ -20030,7 +20030,7 @@
         <v/>
       </c>
       <c r="G517" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H517" t="str">
         <v>Ok</v>
@@ -20068,7 +20068,7 @@
         <v/>
       </c>
       <c r="G518" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H518" t="str">
         <v>Ok</v>
@@ -20106,7 +20106,7 @@
         <v/>
       </c>
       <c r="G519" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H519" t="str">
         <v>Ok</v>
@@ -20144,7 +20144,7 @@
         <v/>
       </c>
       <c r="G520" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H520" t="str">
         <v>Ok</v>
@@ -20182,7 +20182,7 @@
         <v/>
       </c>
       <c r="G521" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H521" t="str">
         <v>Ok</v>
@@ -20220,7 +20220,7 @@
         <v/>
       </c>
       <c r="G522" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H522" t="str">
         <v>Ok</v>
@@ -20258,7 +20258,7 @@
         <v/>
       </c>
       <c r="G523" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H523" t="str">
         <v>Ok</v>
@@ -20296,7 +20296,7 @@
         <v/>
       </c>
       <c r="G524" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H524" t="str">
         <v>Ok</v>
@@ -20334,7 +20334,7 @@
         <v/>
       </c>
       <c r="G525" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H525" t="str">
         <v>Ok</v>
@@ -20372,7 +20372,7 @@
         <v/>
       </c>
       <c r="G526" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H526" t="str">
         <v>Ok</v>
@@ -20410,7 +20410,7 @@
         <v/>
       </c>
       <c r="G527" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H527" t="str">
         <v>Ok</v>
@@ -20448,7 +20448,7 @@
         <v/>
       </c>
       <c r="G528" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H528" t="str">
         <v>Ok</v>
@@ -20486,7 +20486,7 @@
         <v/>
       </c>
       <c r="G529" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H529" t="str">
         <v>Ok</v>
@@ -20524,7 +20524,7 @@
         <v/>
       </c>
       <c r="G530" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H530" t="str">
         <v>Ok</v>
@@ -20562,7 +20562,7 @@
         <v/>
       </c>
       <c r="G531" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H531" t="str">
         <v>Ok</v>
@@ -20600,7 +20600,7 @@
         <v/>
       </c>
       <c r="G532" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H532" t="str">
         <v>NONONO</v>
@@ -20638,7 +20638,7 @@
         <v/>
       </c>
       <c r="G533" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H533" t="str">
         <v>Ok</v>
@@ -20676,7 +20676,7 @@
         <v/>
       </c>
       <c r="G534" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H534" t="str">
         <v>Ok</v>
@@ -20714,7 +20714,7 @@
         <v/>
       </c>
       <c r="G535" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H535" t="str">
         <v>Ok</v>
@@ -20752,7 +20752,7 @@
         <v/>
       </c>
       <c r="G536" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H536" t="str">
         <v>Ok</v>
@@ -20790,7 +20790,7 @@
         <v/>
       </c>
       <c r="G537" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H537" t="str">
         <v>Ok</v>
@@ -20828,7 +20828,7 @@
         <v/>
       </c>
       <c r="G538" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H538" t="str">
         <v>NONONO</v>
@@ -20866,7 +20866,7 @@
         <v/>
       </c>
       <c r="G539" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H539" t="str">
         <v>Ok</v>
@@ -20904,7 +20904,7 @@
         <v/>
       </c>
       <c r="G540" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H540" t="str">
         <v>Ok</v>
@@ -20942,7 +20942,7 @@
         <v/>
       </c>
       <c r="G541" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H541" t="str">
         <v>Ok</v>
@@ -20980,7 +20980,7 @@
         <v/>
       </c>
       <c r="G542" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H542" t="str">
         <v>Ok</v>
@@ -21018,7 +21018,7 @@
         <v/>
       </c>
       <c r="G543" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H543" t="str">
         <v>NONONO</v>
@@ -21056,7 +21056,7 @@
         <v/>
       </c>
       <c r="G544" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H544" t="str">
         <v>Ok</v>
@@ -21094,7 +21094,7 @@
         <v/>
       </c>
       <c r="G545" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H545" t="str">
         <v>Ok</v>
@@ -21132,7 +21132,7 @@
         <v/>
       </c>
       <c r="G546" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H546" t="str">
         <v>Ok</v>
@@ -21170,7 +21170,7 @@
         <v/>
       </c>
       <c r="G547" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H547" t="str">
         <v>Ok</v>
@@ -21208,7 +21208,7 @@
         <v/>
       </c>
       <c r="G548" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H548" t="str">
         <v>Ok</v>
@@ -21246,7 +21246,7 @@
         <v/>
       </c>
       <c r="G549" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H549" t="str">
         <v>Ok</v>
@@ -21284,7 +21284,7 @@
         <v/>
       </c>
       <c r="G550" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H550" t="str">
         <v>Ok</v>
@@ -21322,7 +21322,7 @@
         <v/>
       </c>
       <c r="G551" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H551" t="str">
         <v>NONONO</v>
@@ -21360,7 +21360,7 @@
         <v/>
       </c>
       <c r="G552" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H552" t="str">
         <v>Ok</v>
@@ -21398,7 +21398,7 @@
         <v/>
       </c>
       <c r="G553" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H553" t="str">
         <v>Ok</v>
@@ -21436,7 +21436,7 @@
         <v/>
       </c>
       <c r="G554" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H554" t="str">
         <v>NONONO</v>
@@ -21474,7 +21474,7 @@
         <v/>
       </c>
       <c r="G555" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H555" t="str">
         <v>NONONO</v>
@@ -21512,7 +21512,7 @@
         <v/>
       </c>
       <c r="G556" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H556" t="str">
         <v>Ok</v>
@@ -21550,7 +21550,7 @@
         <v/>
       </c>
       <c r="G557" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H557" t="str">
         <v>Ok</v>
@@ -21588,7 +21588,7 @@
         <v/>
       </c>
       <c r="G558" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H558" t="str">
         <v>Ok</v>
@@ -21626,7 +21626,7 @@
         <v/>
       </c>
       <c r="G559" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H559" t="str">
         <v>Ok</v>
@@ -21664,7 +21664,7 @@
         <v/>
       </c>
       <c r="G560" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H560" t="str">
         <v>Ok</v>
@@ -21702,7 +21702,7 @@
         <v/>
       </c>
       <c r="G561" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H561" t="str">
         <v>Ok</v>
@@ -21854,7 +21854,7 @@
         <v/>
       </c>
       <c r="G565" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H565" t="str">
         <v>Ok</v>
@@ -21892,7 +21892,7 @@
         <v/>
       </c>
       <c r="G566" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H566" t="str">
         <v>Ok</v>
@@ -21930,7 +21930,7 @@
         <v/>
       </c>
       <c r="G567" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H567" t="str">
         <v>Ok</v>
@@ -21968,7 +21968,7 @@
         <v/>
       </c>
       <c r="G568" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H568" t="str">
         <v>Ok</v>
@@ -22120,7 +22120,7 @@
         <v/>
       </c>
       <c r="G572" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H572" t="str">
         <v>Ok</v>
@@ -22158,7 +22158,7 @@
         <v/>
       </c>
       <c r="G573" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H573" t="str">
         <v>Ok</v>
@@ -22196,7 +22196,7 @@
         <v/>
       </c>
       <c r="G574" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H574" t="str">
         <v>Ok</v>
@@ -22234,7 +22234,7 @@
         <v/>
       </c>
       <c r="G575" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H575" t="str">
         <v>Ok</v>
@@ -22462,7 +22462,7 @@
         <v/>
       </c>
       <c r="G581" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H581" t="str">
         <v>Ok</v>
@@ -22500,7 +22500,7 @@
         <v/>
       </c>
       <c r="G582" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H582" t="str">
         <v>Ok</v>
@@ -22538,7 +22538,7 @@
         <v/>
       </c>
       <c r="G583" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H583" t="str">
         <v>Ok</v>
@@ -24412,10 +24412,411 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:B50"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Pokemon Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Can Obtain?</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sprigatito</v>
+      </c>
+      <c r="B2" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Crocalor</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Quaxly</v>
+      </c>
+      <c r="B4" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Quaxwell</v>
+      </c>
+      <c r="B5" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Quaquaval</v>
+      </c>
+      <c r="B6" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Pawmot</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Maushold</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Arboliva</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Garganacl</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Armarouge</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Ceruledge</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Bellibolt</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Mabosstiff</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Brambleghast</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Toedscruel</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Klawf</v>
+      </c>
+      <c r="B17" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Scovillain</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Tinkaton</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Palafin</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Glimmet</v>
+      </c>
+      <c r="B21" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Cetitan</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Veluza</v>
+      </c>
+      <c r="B23" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Annihilape</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Farigiraf</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Dudunsparce</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Kingambit</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Great Tusk</v>
+      </c>
+      <c r="B28" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Brute Bonnet</v>
+      </c>
+      <c r="B29" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Flutter Mane</v>
+      </c>
+      <c r="B30" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Slither Wing</v>
+      </c>
+      <c r="B31" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Iron Treads</v>
+      </c>
+      <c r="B32" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Iron Bundle</v>
+      </c>
+      <c r="B33" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Iron Jugulis</v>
+      </c>
+      <c r="B34" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Iron Moth</v>
+      </c>
+      <c r="B35" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Baxcalibur</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Gimmighoul</v>
+      </c>
+      <c r="B37" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Gholdengo</v>
+      </c>
+      <c r="B38" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Iron Valiant</v>
+      </c>
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Walking Wake</v>
+      </c>
+      <c r="B40" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Iron Leaves</v>
+      </c>
+      <c r="B41" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Dipplin</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Evolve</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Poltchageist</v>
+      </c>
+      <c r="B43" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Sinistcha</v>
+      </c>
+      <c r="B44" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Archaludon</v>
+      </c>
+      <c r="B45" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Hydrapple</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2xEvolution</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Gouging Fire</v>
+      </c>
+      <c r="B47" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Raging Bolt</v>
+      </c>
+      <c r="B48" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Iron Boulder</v>
+      </c>
+      <c r="B49" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Iron Crown</v>
+      </c>
+      <c r="B50" t="str">
+        <v>No</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B50"/>
   </ignoredErrors>
 </worksheet>
 </file>